--- a/03_Outputs/San_Juan/08_Educacion/educacion.xlsx
+++ b/03_Outputs/San_Juan/08_Educacion/educacion.xlsx
@@ -419,8 +419,7 @@
     <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
     <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
     <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="8" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3634,13 +3633,13 @@
         <v>2021</v>
       </c>
       <c r="F98" s="7">
-        <v>0.842551876417312</v>
+        <v>0.817945637432188</v>
       </c>
       <c r="G98" s="9">
-        <v>0.00617420862040771</v>
+        <v>0.0723540461121157</v>
       </c>
       <c r="H98" s="11">
-        <v>0.159042047883711</v>
+        <v>0.0801244620253165</v>
       </c>
     </row>
     <row r="99">
@@ -3668,13 +3667,13 @@
         <v>2021</v>
       </c>
       <c r="F99" s="7">
-        <v>0.872001779366615</v>
+        <v>0.793502501294906</v>
       </c>
       <c r="G99" s="9">
-        <v>0.0186323709192612</v>
+        <v>0.0629997086090639</v>
       </c>
       <c r="H99" s="11">
-        <v>0.111149943064852</v>
+        <v>0.0713185398011997</v>
       </c>
     </row>
     <row r="100">
@@ -3702,13 +3701,13 @@
         <v>2021</v>
       </c>
       <c r="F100" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G100" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H100" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="101">
